--- a/src/ExcelsiorAspose.Tests/IncludeTests.ExcludeOne.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/IncludeTests.ExcludeOne.verified.xlsx
@@ -482,7 +482,7 @@
     <col min="2" max="2" width="14.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14" customHeight="1">
+    <row r="1" spans="1:2" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,7 +490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14" customHeight="1">
+    <row r="2" spans="1:2" ht="16" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14" customHeight="1">
+    <row r="3" spans="1:2" ht="16" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/IncludeTests.ExcludeOne.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/IncludeTests.ExcludeOne.verified.xlsx
@@ -482,7 +482,7 @@
     <col min="2" max="2" width="14.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" customHeight="1">
+    <row r="1" spans="1:2" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,7 +490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" customHeight="1">
+    <row r="2" spans="1:2" ht="14" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16" customHeight="1">
+    <row r="3" spans="1:2" ht="14" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
